--- a/input/input_exp_He-Xe-T20.xlsx
+++ b/input/input_exp_He-Xe-T20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/izg5132_psu_edu/Documents/06_PHD_EME_PSU/00 RESEARCH/PHD UHS PROJECT/MATLAB-GITHUB/UHS-CT-Dispersion-Exps-Analog/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="859" documentId="11_F25DC773A252ABDACC1048B8D1997AFC5ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6167C30C-7414-490A-B314-B21EDD0FBDE4}"/>
+  <xr:revisionPtr revIDLastSave="879" documentId="11_F25DC773A252ABDACC1048B8D1997AFC5ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95865EFD-71D3-4B21-8EF6-A242F8AFC89F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="2235" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="90">
   <si>
     <t>path</t>
   </si>
@@ -251,9 +251,6 @@
     <t>CT_Day4_HP_HQ-12-18-25.dat</t>
   </si>
   <si>
-    <t>CTfolder</t>
-  </si>
-  <si>
     <t>data/CF-CT-He-Xe-T20-P900-V-Q1/</t>
   </si>
   <si>
@@ -266,7 +263,49 @@
     <t>data/CF-CT-He-Xe-T20-P725-V-Q5/</t>
   </si>
   <si>
-    <t>16Dec25/</t>
+    <t>CT_data_exp</t>
+  </si>
+  <si>
+    <t>CT_data_ref_init</t>
+  </si>
+  <si>
+    <t>CT_data_ref_final</t>
+  </si>
+  <si>
+    <t>18Dec25/exp/</t>
+  </si>
+  <si>
+    <t>18Dec25/refXe/</t>
+  </si>
+  <si>
+    <t>18Dec25/refHe/</t>
+  </si>
+  <si>
+    <t>17Dec25/exp/</t>
+  </si>
+  <si>
+    <t>17Dec25/refXe/</t>
+  </si>
+  <si>
+    <t>17Dec25/refHe/</t>
+  </si>
+  <si>
+    <t>19Dec25/exp/</t>
+  </si>
+  <si>
+    <t>19Dec25/refXe/</t>
+  </si>
+  <si>
+    <t>19Dec25/refHe/</t>
+  </si>
+  <si>
+    <t>16Dec25/exp/</t>
+  </si>
+  <si>
+    <t>16Dec25/refXe/</t>
+  </si>
+  <si>
+    <t>16Dec25/refHe/</t>
   </si>
 </sst>
 </file>
@@ -607,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
@@ -630,7 +669,7 @@
     <col min="35" max="35" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -737,10 +776,16 @@
         <v>20</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
@@ -796,7 +841,7 @@
       <c r="AG2" s="1"/>
       <c r="AH2" s="1"/>
     </row>
-    <row r="3" spans="1:36" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -882,7 +927,7 @@
         <v>1</v>
       </c>
       <c r="AC3" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AD3" s="5" t="s">
         <v>53</v>
@@ -893,8 +938,17 @@
       <c r="AF3" s="5" t="s">
         <v>55</v>
       </c>
+      <c r="AJ3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="4" spans="1:36" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>56</v>
       </c>
@@ -980,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="AC4" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AD4" s="5" t="s">
         <v>70</v>
@@ -991,8 +1045,17 @@
       <c r="AF4" s="5" t="s">
         <v>59</v>
       </c>
+      <c r="AJ4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="5" spans="1:36" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -1078,7 +1141,7 @@
         <v>1</v>
       </c>
       <c r="AC5" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AD5" s="5" t="s">
         <v>62</v>
@@ -1089,8 +1152,17 @@
       <c r="AF5" s="5" t="s">
         <v>64</v>
       </c>
+      <c r="AJ5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="6" spans="1:36" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -1176,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="AC6" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AD6" s="5" t="s">
         <v>67</v>
@@ -1188,7 +1260,13 @@
         <v>69</v>
       </c>
       <c r="AJ6" t="s">
-        <v>76</v>
+        <v>87</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
